--- a/generated/spreadsheet/verbose/outline-planning-outline-verbose.xlsx
+++ b/generated/spreadsheet/verbose/outline-planning-outline-verbose.xlsx
@@ -1024,7 +1024,7 @@
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>List of codelist references that the document covers</t>
+          <t>Planning requirement references identifying the information this document provides. A document may address more than one requirement. These references identify its coverage; they do not establish that the requirements have been satisfied.</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -6861,7 +6861,7 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Planning officer name</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr"/>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>unit-type</t>
+          <t>capacity-unit</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>Unit type</t>
+          <t>Capacity unit</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr"/>
@@ -7229,7 +7229,7 @@
       <c r="K135" s="2" t="inlineStr"/>
       <c r="L135" s="2" t="inlineStr">
         <is>
-          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
+          <t>Unit used to express the total capacity of a waste management facility</t>
         </is>
       </c>
       <c r="M135" s="2" t="inlineStr">
@@ -7313,12 +7313,12 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>unit-type</t>
+          <t>throughput-unit</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>Unit type</t>
+          <t>Throughput unit</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr"/>
@@ -7327,7 +7327,7 @@
       <c r="K137" s="2" t="inlineStr"/>
       <c r="L137" s="2" t="inlineStr">
         <is>
-          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
+          <t>Unit used to express the annual throughput of a waste management facility</t>
         </is>
       </c>
       <c r="M137" s="2" t="inlineStr">
@@ -7571,7 +7571,7 @@
       <c r="K142" s="2" t="inlineStr"/>
       <c r="L142" s="2" t="inlineStr">
         <is>
-          <t>A description of what is being proposed, including the development, works, or change of use</t>
+          <t>A description of the development, works, change of use or reserved matters for which approval is sought</t>
         </is>
       </c>
       <c r="M142" s="2" t="inlineStr">
